--- a/Analysis/Output/raw_attributes_dictionary.xlsx
+++ b/Analysis/Output/raw_attributes_dictionary.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,12 +418,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>Date of Interview</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E3">
@@ -436,16 +436,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>age</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -454,7 +454,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agegrps</t>
+          <t>study</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>Agegrps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>marstat</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HHead</t>
+          <t>marstat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Activitylevel</t>
+          <t>HHead</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SocialMedia</t>
+          <t>Activitylevel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supportive</t>
+          <t>SocialMedia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Incomesource</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Incomesource</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MHServices</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -634,12 +634,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nervous</t>
+          <t>MHServices</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E15">
@@ -652,7 +652,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Worrying</t>
+          <t>Nervous</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Things</t>
+          <t>Worrying</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Trouble</t>
+          <t>Things</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Restless</t>
+          <t>Trouble</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Irritable</t>
+          <t>Restless</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Afraid</t>
+          <t>Irritable</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GAD</t>
+          <t>Afraid</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GADcategory</t>
+          <t>GAD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E23">
@@ -796,12 +796,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>GADcategory</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E24">
@@ -814,7 +814,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hopeless</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sleeping</t>
+          <t>Hopeless</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tired</t>
+          <t>Sleeping</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Appetite</t>
+          <t>Tired</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Appetite</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Concentrating</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Moving</t>
+          <t>Concentrating</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Thoughts</t>
+          <t>Moving</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PHQ</t>
+          <t>Thoughts</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -976,12 +976,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PHQcat</t>
+          <t>PHQ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E34">
@@ -994,12 +994,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hypomania</t>
+          <t>PHQcat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E35">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hypomania2</t>
+          <t>Hypomania</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Thoughtinsertion</t>
+          <t>Hypomania2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Thoughtinsertion2</t>
+          <t>Thoughtinsertion</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Paranoia</t>
+          <t>Thoughtinsertion2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Paranoia2</t>
+          <t>Paranoia</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Strangeexperiences</t>
+          <t>Paranoia2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Strangeexperiences2</t>
+          <t>Strangeexperiences</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hallucinations</t>
+          <t>Strangeexperiences2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hallucinations2</t>
+          <t>Hallucinations</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Psychosis</t>
+          <t>Hallucinations2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E45">
@@ -1192,15 +1192,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Psychosis</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>chr</t>
+        </is>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Psychosis_Numeric</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>dbl</t>
-        </is>
-      </c>
-      <c r="E46">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>dbl</t>
+        </is>
+      </c>
+      <c r="E47">
         <v>0</v>
       </c>
     </row>
@@ -1211,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1275,12 +1293,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>date_of_interview</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E3">
@@ -1293,16 +1311,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>age</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1311,7 +1329,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>agegrps</t>
+          <t>study</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1329,7 +1347,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>agegrps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1347,7 +1365,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>marstat</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1365,7 +1383,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>h_head</t>
+          <t>marstat</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1383,7 +1401,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>activitylevel</t>
+          <t>h_head</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1401,7 +1419,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>activitylevel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1419,7 +1437,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>supportive</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1437,7 +1455,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>incomesource</t>
+          <t>supportive</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1455,7 +1473,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>incomesource</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1473,7 +1491,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mh_services</t>
+          <t>awareness</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1491,12 +1509,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nervous</t>
+          <t>mh_services</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E15">
@@ -1509,7 +1527,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>worrying</t>
+          <t>nervous</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1527,7 +1545,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>things</t>
+          <t>worrying</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1545,7 +1563,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>trouble</t>
+          <t>things</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1563,7 +1581,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>restless</t>
+          <t>trouble</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1581,7 +1599,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>irritable</t>
+          <t>restless</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1599,7 +1617,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>afraid</t>
+          <t>irritable</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1617,7 +1635,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gad</t>
+          <t>afraid</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1635,12 +1653,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ga_dcategory</t>
+          <t>gad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E23">
@@ -1653,12 +1671,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>interest</t>
+          <t>ga_dcategory</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E24">
@@ -1671,7 +1689,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hopeless</t>
+          <t>interest</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1689,7 +1707,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sleeping</t>
+          <t>hopeless</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1707,7 +1725,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>tired</t>
+          <t>sleeping</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1725,7 +1743,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>appetite</t>
+          <t>tired</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1743,7 +1761,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>appetite</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1761,7 +1779,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>concentrating</t>
+          <t>family</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1779,7 +1797,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>moving</t>
+          <t>concentrating</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1797,7 +1815,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>thoughts</t>
+          <t>moving</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1815,7 +1833,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>phq</t>
+          <t>thoughts</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1833,12 +1851,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ph_qcat</t>
+          <t>phq</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E34">
@@ -1851,12 +1869,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>hypomania</t>
+          <t>ph_qcat</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E35">
@@ -1869,7 +1887,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>hypomania2</t>
+          <t>hypomania</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1887,7 +1905,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>thoughtinsertion</t>
+          <t>hypomania2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1905,7 +1923,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>thoughtinsertion2</t>
+          <t>thoughtinsertion</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1923,7 +1941,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>paranoia</t>
+          <t>thoughtinsertion2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1941,7 +1959,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>paranoia2</t>
+          <t>paranoia</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1959,7 +1977,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>strangeexperiences</t>
+          <t>paranoia2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1977,7 +1995,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>strangeexperiences2</t>
+          <t>strangeexperiences</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1995,7 +2013,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>hallucinations</t>
+          <t>strangeexperiences2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2013,7 +2031,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>hallucinations2</t>
+          <t>hallucinations</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2031,12 +2049,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>psychosis</t>
+          <t>hallucinations2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E45">
@@ -2049,15 +2067,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>psychosis</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>chr</t>
+        </is>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>psychosis_numeric</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>dbl</t>
-        </is>
-      </c>
-      <c r="E46">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>dbl</t>
+        </is>
+      </c>
+      <c r="E47">
         <v>0</v>
       </c>
     </row>
@@ -2068,7 +2104,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2132,12 +2168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>Date of Interview</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E3">
@@ -2150,12 +2186,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Agegrps</t>
+          <t>age</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E4">
@@ -2168,7 +2204,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>Agegrps</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2186,7 +2222,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>marstat</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2204,7 +2240,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>marstat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2213,7 +2249,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2222,7 +2258,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HHead</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2231,7 +2267,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -2240,7 +2276,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Activitylevel</t>
+          <t>HHead</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2249,7 +2285,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -2258,7 +2294,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SocialMedia</t>
+          <t>Activitylevel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2276,12 +2312,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nervous</t>
+          <t>SocialMedia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E11">
@@ -2294,7 +2330,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Worrying</t>
+          <t>Nervous</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2312,7 +2348,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Things</t>
+          <t>Worrying</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2330,7 +2366,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trouble</t>
+          <t>Things</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2348,7 +2384,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Restless</t>
+          <t>Trouble</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2366,7 +2402,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Irritable</t>
+          <t>Restless</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2384,7 +2420,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Afraid</t>
+          <t>Irritable</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2402,7 +2438,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GAD</t>
+          <t>Afraid</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2420,7 +2456,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>GAD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2438,7 +2474,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hopeless</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2456,7 +2492,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sleeping</t>
+          <t>Hopeless</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2474,7 +2510,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tired</t>
+          <t>Sleeping</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2492,7 +2528,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Appetite</t>
+          <t>Tired</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2510,7 +2546,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Appetite</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2528,7 +2564,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Concentrating</t>
+          <t>Family</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2546,7 +2582,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Moving</t>
+          <t>Concentrating</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2564,7 +2600,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thoughts</t>
+          <t>Moving</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2582,7 +2618,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PHQ</t>
+          <t>Thoughts</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2600,7 +2636,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hypomania</t>
+          <t>PHQ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2618,7 +2654,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hypomania2</t>
+          <t>Hypomania</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2636,7 +2672,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Thoughtinsertion</t>
+          <t>Hypomania2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2654,7 +2690,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Thoughtinsertion2</t>
+          <t>Thoughtinsertion</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2672,7 +2708,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paranoia</t>
+          <t>Thoughtinsertion2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2690,7 +2726,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Paranoia2</t>
+          <t>Paranoia</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2708,7 +2744,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Strangeexperiences</t>
+          <t>Paranoia2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2726,7 +2762,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Strangeexperiences2</t>
+          <t>Strangeexperiences</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2744,7 +2780,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hallucinations</t>
+          <t>Strangeexperiences2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2762,7 +2798,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hallucinations2</t>
+          <t>Hallucinations</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2780,7 +2816,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PSQ</t>
+          <t>Hallucinations2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2798,12 +2834,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GAD_Category</t>
+          <t>PSQ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E40">
@@ -2816,7 +2852,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PHQ_Category</t>
+          <t>GAD_Category</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2834,15 +2870,33 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>PHQ_Category</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>chr</t>
+        </is>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>PSQ_totals</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>chr</t>
-        </is>
-      </c>
-      <c r="E42">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>chr</t>
+        </is>
+      </c>
+      <c r="E43">
         <v>0</v>
       </c>
     </row>
@@ -2853,7 +2907,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2917,12 +2971,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>date_of_interview</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E3">
@@ -2935,12 +2989,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>agegrps</t>
+          <t>age</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E4">
@@ -2953,7 +3007,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>agegrps</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2971,7 +3025,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>marstat</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2989,7 +3043,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>education</t>
+          <t>marstat</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2998,7 +3052,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3007,7 +3061,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>h_head</t>
+          <t>education</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3016,7 +3070,7 @@
         </is>
       </c>
       <c r="E8">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -3025,7 +3079,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>activitylevel</t>
+          <t>h_head</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3034,7 +3088,7 @@
         </is>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -3043,7 +3097,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>activitylevel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3061,12 +3115,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nervous</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>dbl</t>
+          <t>chr</t>
         </is>
       </c>
       <c r="E11">
@@ -3079,7 +3133,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>worrying</t>
+          <t>nervous</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3097,7 +3151,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>things</t>
+          <t>worrying</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3115,7 +3169,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>trouble</t>
+          <t>things</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3133,7 +3187,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>restless</t>
+          <t>trouble</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3151,7 +3205,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>irritable</t>
+          <t>restless</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3169,7 +3223,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>afraid</t>
+          <t>irritable</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3187,7 +3241,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gad</t>
+          <t>afraid</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3205,7 +3259,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>interest</t>
+          <t>gad</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3223,7 +3277,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hopeless</t>
+          <t>interest</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3241,7 +3295,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sleeping</t>
+          <t>hopeless</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3259,7 +3313,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tired</t>
+          <t>sleeping</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3277,7 +3331,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>appetite</t>
+          <t>tired</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3295,7 +3349,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>appetite</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3313,7 +3367,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>concentrating</t>
+          <t>family</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3331,7 +3385,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>moving</t>
+          <t>concentrating</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3349,7 +3403,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>thoughts</t>
+          <t>moving</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3367,7 +3421,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>phq</t>
+          <t>thoughts</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3385,7 +3439,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hypomania</t>
+          <t>phq</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3403,7 +3457,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hypomania2</t>
+          <t>hypomania</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3421,7 +3475,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>thoughtinsertion</t>
+          <t>hypomania2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3439,7 +3493,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>thoughtinsertion2</t>
+          <t>thoughtinsertion</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3457,7 +3511,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>paranoia</t>
+          <t>thoughtinsertion2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3475,7 +3529,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>paranoia2</t>
+          <t>paranoia</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3493,7 +3547,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>strangeexperiences</t>
+          <t>paranoia2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3511,7 +3565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>strangeexperiences2</t>
+          <t>strangeexperiences</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3529,7 +3583,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hallucinations</t>
+          <t>strangeexperiences2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3547,7 +3601,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>hallucinations2</t>
+          <t>hallucinations</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3565,7 +3619,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>psq</t>
+          <t>hallucinations2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3583,12 +3637,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gad_category</t>
+          <t>psq</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>chr</t>
+          <t>dbl</t>
         </is>
       </c>
       <c r="E40">
@@ -3601,7 +3655,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>phq_category</t>
+          <t>gad_category</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3619,15 +3673,33 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>phq_category</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>chr</t>
+        </is>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>psq_totals</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>chr</t>
-        </is>
-      </c>
-      <c r="E42">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>chr</t>
+        </is>
+      </c>
+      <c r="E43">
         <v>0</v>
       </c>
     </row>
